--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="371">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -322,10 +322,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DeviceRequest.implicitRules</t>
   </si>
   <si>
@@ -345,6 +352,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceRequest.language</t>
   </si>
   <si>
@@ -422,9 +432,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DeviceRequest.extension</t>
   </si>
   <si>
@@ -445,6 +452,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -549,6 +566,13 @@
     <t>Plan/proposal/order fulfilled by this request.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Request.basedOn</t>
   </si>
   <si>
@@ -646,6 +670,9 @@
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>order</t>
   </si>
   <si>
@@ -757,9 +784,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DeviceRequest.parameter.extension</t>
   </si>
   <si>
@@ -799,6 +823,9 @@
     <t>A code or string that identifies the device detail being asserted.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>A code that identifies the device detail.</t>
   </si>
   <si>
@@ -1101,6 +1128,9 @@
   </si>
   <si>
     <t>Details about this request that were not represented at all or sufficiently in one of the attributes provided in a class. These may include for example a comment, an instruction, or a note associated with the statement.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1469,7 +1499,7 @@
     <col min="26" max="26" width="39.265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.1875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1934,10 +1964,10 @@
         <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -1946,7 +1976,7 @@
         <v>78</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>78</v>
@@ -1957,10 +1987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1983,16 +2013,16 @@
         <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2042,7 +2072,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -2051,10 +2081,10 @@
         <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>78</v>
@@ -2063,7 +2093,7 @@
         <v>78</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>78</v>
@@ -2074,10 +2104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2100,16 +2130,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2135,13 +2165,13 @@
         <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>78</v>
@@ -2159,7 +2189,7 @@
         <v>78</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
@@ -2168,10 +2198,10 @@
         <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -2180,7 +2210,7 @@
         <v>78</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>78</v>
@@ -2191,14 +2221,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2217,16 +2247,16 @@
         <v>78</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2276,7 +2306,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
@@ -2285,10 +2315,10 @@
         <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -2297,7 +2327,7 @@
         <v>78</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2308,14 +2338,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2334,16 +2364,16 @@
         <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2393,7 +2423,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2414,7 +2444,7 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2425,14 +2455,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2451,16 +2481,16 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2498,19 +2528,19 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2519,10 +2549,10 @@
         <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2531,7 +2561,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2542,14 +2572,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2568,19 +2598,19 @@
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2617,19 +2647,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2638,10 +2668,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2650,7 +2680,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2661,10 +2691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2687,13 +2717,13 @@
         <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2744,7 +2774,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2753,33 +2783,33 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2802,16 +2832,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2861,7 +2891,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2870,19 +2900,19 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -2893,10 +2923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2919,16 +2949,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2978,7 +3008,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2987,19 +3017,19 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3010,10 +3040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3036,15 +3066,17 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3093,7 +3125,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3102,33 +3134,33 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3151,15 +3183,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3208,7 +3242,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3217,19 +3251,19 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3240,10 +3274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3266,13 +3300,13 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3323,7 +3357,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3332,19 +3366,19 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3355,10 +3389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3381,16 +3415,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3416,13 +3450,13 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3440,7 +3474,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3449,33 +3483,33 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3498,15 +3532,17 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3516,7 +3552,7 @@
         <v>78</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>78</v>
@@ -3531,13 +3567,13 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
@@ -3555,7 +3591,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3564,22 +3600,22 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -3587,10 +3623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3613,21 +3649,23 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q19" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="R19" t="s" s="2">
         <v>78</v>
@@ -3648,13 +3686,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3672,7 +3710,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3681,22 +3719,22 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -3704,10 +3742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3730,13 +3768,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3763,13 +3801,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3787,7 +3825,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -3796,33 +3834,33 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3845,13 +3883,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3902,7 +3940,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3911,33 +3949,33 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3960,13 +3998,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4017,7 +4055,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4038,7 +4076,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4049,14 +4087,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4075,16 +4113,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4122,19 +4160,19 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4143,10 +4181,10 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4155,7 +4193,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4166,14 +4204,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4192,19 +4230,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4253,7 +4291,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4262,10 +4300,10 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4274,7 +4312,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4285,10 +4323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4311,15 +4349,17 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4344,10 +4384,10 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>78</v>
@@ -4368,7 +4408,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4377,33 +4417,33 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4426,16 +4466,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4485,7 +4525,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4494,33 +4534,33 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4543,15 +4583,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4600,7 +4642,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>89</v>
@@ -4609,33 +4651,33 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4658,15 +4700,17 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4715,7 +4759,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4724,33 +4768,33 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4773,13 +4817,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4830,7 +4874,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4839,33 +4883,33 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4888,13 +4932,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4945,7 +4989,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4954,33 +4998,33 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5003,15 +5047,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5060,7 +5106,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5069,22 +5115,22 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5092,10 +5138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5118,15 +5164,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5151,13 +5199,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5175,7 +5223,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5184,22 +5232,22 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5207,10 +5255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5233,15 +5281,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5290,7 +5340,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5299,22 +5349,22 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5322,10 +5372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5348,15 +5398,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5381,13 +5433,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5405,7 +5457,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5414,33 +5466,33 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5463,15 +5515,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5520,7 +5574,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5529,22 +5583,22 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -5552,10 +5606,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5578,15 +5632,17 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5635,7 +5691,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5644,19 +5700,19 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5667,10 +5723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5693,17 +5749,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5752,7 +5810,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5761,19 +5819,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5784,10 +5842,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5810,15 +5868,17 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5867,7 +5927,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5876,33 +5936,33 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5925,16 +5985,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5984,7 +6044,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5993,19 +6053,19 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -322,17 +322,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DeviceRequest.implicitRules</t>
   </si>
   <si>
@@ -352,9 +345,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DeviceRequest.language</t>
   </si>
   <si>
@@ -432,6 +422,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DeviceRequest.extension</t>
   </si>
   <si>
@@ -452,16 +445,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -566,13 +549,6 @@
     <t>Plan/proposal/order fulfilled by this request.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Request.basedOn</t>
   </si>
   <si>
@@ -670,9 +646,6 @@
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>order</t>
   </si>
   <si>
@@ -784,6 +757,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceRequest.parameter.extension</t>
   </si>
   <si>
@@ -823,9 +799,6 @@
     <t>A code or string that identifies the device detail being asserted.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>A code that identifies the device detail.</t>
   </si>
   <si>
@@ -1128,9 +1101,6 @@
   </si>
   <si>
     <t>Details about this request that were not represented at all or sufficiently in one of the attributes provided in a class. These may include for example a comment, an instruction, or a note associated with the statement.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1499,7 +1469,7 @@
     <col min="26" max="26" width="39.265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.1875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1964,11 +1934,11 @@
         <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
       </c>
@@ -1976,7 +1946,7 @@
         <v>78</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>78</v>
@@ -1987,10 +1957,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2013,16 +1983,16 @@
         <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2072,7 +2042,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -2081,11 +2051,11 @@
         <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>78</v>
       </c>
@@ -2093,7 +2063,7 @@
         <v>78</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>78</v>
@@ -2104,10 +2074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2130,16 +2100,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2165,31 +2135,31 @@
         <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
@@ -2198,11 +2168,11 @@
         <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2210,7 +2180,7 @@
         <v>78</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>78</v>
@@ -2221,14 +2191,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2247,16 +2217,16 @@
         <v>78</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2306,7 +2276,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
@@ -2315,11 +2285,11 @@
         <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
       </c>
@@ -2327,7 +2297,7 @@
         <v>78</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2338,14 +2308,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2364,16 +2334,16 @@
         <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2423,7 +2393,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2444,7 +2414,7 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2455,14 +2425,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2481,16 +2451,16 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2528,19 +2498,19 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2549,10 +2519,10 @@
         <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2561,7 +2531,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2572,14 +2542,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2598,19 +2568,19 @@
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2647,19 +2617,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2668,10 +2638,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2680,7 +2650,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2691,10 +2661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2717,13 +2687,13 @@
         <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2774,7 +2744,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2783,33 +2753,33 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2832,16 +2802,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2891,7 +2861,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2900,19 +2870,19 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -2923,10 +2893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2949,16 +2919,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3008,7 +2978,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3017,19 +2987,19 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3040,10 +3010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3066,17 +3036,15 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3125,7 +3093,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3134,33 +3102,33 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3183,17 +3151,15 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3242,7 +3208,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3251,19 +3217,19 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3274,10 +3240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3300,13 +3266,13 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3357,7 +3323,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3366,19 +3332,19 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3389,10 +3355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3415,16 +3381,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3450,13 +3416,13 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3474,7 +3440,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3483,33 +3449,33 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3532,17 +3498,15 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3552,7 +3516,7 @@
         <v>78</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>78</v>
@@ -3567,13 +3531,13 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
@@ -3591,7 +3555,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3600,22 +3564,22 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -3623,10 +3587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3649,23 +3613,21 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q19" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="R19" t="s" s="2">
         <v>78</v>
@@ -3686,13 +3648,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3710,7 +3672,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3719,22 +3681,22 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK19" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -3742,10 +3704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3768,13 +3730,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3801,13 +3763,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3825,7 +3787,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -3834,33 +3796,33 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3883,13 +3845,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3940,7 +3902,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3949,33 +3911,33 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3998,13 +3960,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4055,7 +4017,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4076,7 +4038,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4087,14 +4049,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4113,16 +4075,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4160,19 +4122,19 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4181,10 +4143,10 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4193,7 +4155,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4204,14 +4166,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4230,19 +4192,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4291,7 +4253,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4300,10 +4262,10 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4312,7 +4274,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4323,10 +4285,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4349,17 +4311,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4384,10 +4344,10 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>78</v>
@@ -4408,7 +4368,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4417,33 +4377,33 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4466,16 +4426,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4525,7 +4485,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4534,33 +4494,33 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4583,17 +4543,15 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4642,7 +4600,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>89</v>
@@ -4651,33 +4609,33 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4700,17 +4658,15 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4759,7 +4715,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4768,33 +4724,33 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4817,13 +4773,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4874,7 +4830,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4883,33 +4839,33 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4932,13 +4888,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4989,7 +4945,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4998,33 +4954,33 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5047,17 +5003,15 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5106,7 +5060,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5115,22 +5069,22 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5138,10 +5092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5164,17 +5118,15 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5199,13 +5151,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5223,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5232,22 +5184,22 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5255,10 +5207,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5281,17 +5233,15 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5340,7 +5290,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5349,22 +5299,22 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM33" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5372,10 +5322,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5398,17 +5348,15 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5433,13 +5381,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5457,7 +5405,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5466,33 +5414,33 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5515,17 +5463,15 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5574,7 +5520,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5583,22 +5529,22 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -5606,10 +5552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5632,17 +5578,15 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5691,7 +5635,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5700,19 +5644,19 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5723,10 +5667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5749,19 +5693,17 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5810,7 +5752,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5819,19 +5761,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5842,10 +5784,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5868,17 +5810,15 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5927,7 +5867,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5936,33 +5876,33 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5985,16 +5925,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6044,7 +5984,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6053,19 +5993,19 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicerequest.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicerequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="371">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -322,10 +322,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DeviceRequest.implicitRules</t>
   </si>
   <si>
@@ -345,6 +352,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceRequest.language</t>
   </si>
   <si>
@@ -422,9 +432,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DeviceRequest.extension</t>
   </si>
   <si>
@@ -445,6 +452,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -549,6 +566,13 @@
     <t>Plan/proposal/order fulfilled by this request.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Request.basedOn</t>
   </si>
   <si>
@@ -646,6 +670,9 @@
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>order</t>
   </si>
   <si>
@@ -757,9 +784,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DeviceRequest.parameter.extension</t>
   </si>
   <si>
@@ -799,6 +823,9 @@
     <t>A code or string that identifies the device detail being asserted.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>A code that identifies the device detail.</t>
   </si>
   <si>
@@ -1101,6 +1128,9 @@
   </si>
   <si>
     <t>Details about this request that were not represented at all or sufficiently in one of the attributes provided in a class. These may include for example a comment, an instruction, or a note associated with the statement.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1469,7 +1499,7 @@
     <col min="26" max="26" width="39.265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.1875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1934,10 +1964,10 @@
         <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -1946,7 +1976,7 @@
         <v>78</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>78</v>
@@ -1957,10 +1987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1983,16 +2013,16 @@
         <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2042,7 +2072,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
@@ -2051,10 +2081,10 @@
         <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>78</v>
@@ -2063,7 +2093,7 @@
         <v>78</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>78</v>
@@ -2074,10 +2104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2100,16 +2130,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2135,13 +2165,13 @@
         <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>78</v>
@@ -2159,7 +2189,7 @@
         <v>78</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
@@ -2168,10 +2198,10 @@
         <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -2180,7 +2210,7 @@
         <v>78</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>78</v>
@@ -2191,14 +2221,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2217,16 +2247,16 @@
         <v>78</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2276,7 +2306,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
@@ -2285,10 +2315,10 @@
         <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -2297,7 +2327,7 @@
         <v>78</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2308,14 +2338,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2334,16 +2364,16 @@
         <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2393,7 +2423,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2414,7 +2444,7 @@
         <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2425,14 +2455,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2451,16 +2481,16 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2498,19 +2528,19 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2519,10 +2549,10 @@
         <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2531,7 +2561,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2542,14 +2572,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2568,19 +2598,19 @@
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2617,19 +2647,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2638,10 +2668,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2650,7 +2680,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2661,10 +2691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2687,13 +2717,13 @@
         <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2744,7 +2774,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2753,33 +2783,33 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2802,16 +2832,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2861,7 +2891,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2870,19 +2900,19 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -2893,10 +2923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2919,16 +2949,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2978,7 +3008,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2987,19 +3017,19 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3010,10 +3040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3036,15 +3066,17 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3093,7 +3125,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3102,33 +3134,33 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3151,15 +3183,17 @@
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3208,7 +3242,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3217,19 +3251,19 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3240,10 +3274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3266,13 +3300,13 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3323,7 +3357,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3332,19 +3366,19 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3355,10 +3389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3381,16 +3415,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3416,13 +3450,13 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3440,7 +3474,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3449,33 +3483,33 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3498,15 +3532,17 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3516,7 +3552,7 @@
         <v>78</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>78</v>
@@ -3531,13 +3567,13 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
@@ -3555,7 +3591,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3564,22 +3600,22 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -3587,10 +3623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3613,21 +3649,23 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q19" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="R19" t="s" s="2">
         <v>78</v>
@@ -3648,13 +3686,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3672,7 +3710,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3681,22 +3719,22 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -3704,10 +3742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3730,13 +3768,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3763,13 +3801,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3787,7 +3825,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -3796,33 +3834,33 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3845,13 +3883,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3902,7 +3940,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3911,33 +3949,33 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3960,13 +3998,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4017,7 +4055,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4038,7 +4076,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4049,14 +4087,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4075,16 +4113,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4122,19 +4160,19 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4143,10 +4181,10 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4155,7 +4193,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>103</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4166,14 +4204,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4192,19 +4230,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4253,7 +4291,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4262,10 +4300,10 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4274,7 +4312,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4285,10 +4323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4311,15 +4349,17 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4344,10 +4384,10 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>78</v>
@@ -4368,7 +4408,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4377,33 +4417,33 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4426,16 +4466,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4485,7 +4525,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4494,33 +4534,33 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4543,15 +4583,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4600,7 +4642,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>89</v>
@@ -4609,33 +4651,33 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4658,15 +4700,17 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4715,7 +4759,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4724,33 +4768,33 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4773,13 +4817,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4830,7 +4874,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4839,33 +4883,33 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4888,13 +4932,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4945,7 +4989,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4954,33 +4998,33 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5003,15 +5047,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5060,7 +5106,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5069,22 +5115,22 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5092,10 +5138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5118,15 +5164,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5151,13 +5199,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5175,7 +5223,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5184,22 +5232,22 @@
         <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5207,10 +5255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5233,15 +5281,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5290,7 +5340,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5299,22 +5349,22 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -5322,10 +5372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5348,15 +5398,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5381,13 +5433,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5405,7 +5457,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5414,33 +5466,33 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5463,15 +5515,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5520,7 +5574,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5529,22 +5583,22 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -5552,10 +5606,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5578,15 +5632,17 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5635,7 +5691,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5644,19 +5700,19 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5667,10 +5723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5693,17 +5749,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5752,7 +5810,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5761,19 +5819,19 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5784,10 +5842,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5810,15 +5868,17 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5867,7 +5927,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5876,33 +5936,33 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5925,16 +5985,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5984,7 +6044,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5993,19 +6053,19 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
